--- a/Assessment Questions/CDA/PYF-110/PYTHON DATA STRUCTURES/List Methods/List_Methods.xlsx
+++ b/Assessment Questions/CDA/PYF-110/PYTHON DATA STRUCTURES/List Methods/List_Methods.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List_Methods" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,11 +454,6 @@
           <t>A) add element B) remove C) sort D) none</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -476,11 +471,6 @@
           <t>A) remove last B) add C) sort D) none</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,7 +490,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -520,11 +510,6 @@
           <t>A) length B) type C) value D) none</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -544,7 +529,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -566,7 +551,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -586,11 +571,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -610,7 +590,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -630,11 +610,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -654,7 +629,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -674,11 +649,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -698,7 +668,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -718,11 +688,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,7 +707,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -762,11 +727,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -784,11 +744,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -808,7 +763,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -830,7 +785,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -850,11 +805,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -874,7 +824,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
